--- a/sofortpdf-google-ads-assets.xlsx
+++ b/sofortpdf-google-ads-assets.xlsx
@@ -2010,7 +2010,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Ab 0,69 € statt 23,99 €/mo</t>
+          <t>PDF-Tools ab nur 0,69 €</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="AJ12" s="2" t="inlineStr">
         <is>
-          <t>Warum 23,99 €/Monat für Adobe zahlen? sofortpdf bietet 19 PDF-Tools ab 0,69 €. Server in der EU. DSGVO-konform.</t>
+          <t>Warum ein teures Adobe-Abo zahlen? sofortpdf bietet 19 PDF-Tools ab 0,69 €. Server in der EU. DSGVO-konform.</t>
         </is>
       </c>
       <c r="AK12" s="2" t="inlineStr">
